--- a/AnalisisFinanciero/data/890903939_2024-12-31_Informacion_Circular_Basica_Juridica_capitulos_X_XIII_traduccion.xlsx
+++ b/AnalisisFinanciero/data/890903939_2024-12-31_Informacion_Circular_Basica_Juridica_capitulos_X_XIII_traduccion.xlsx
@@ -1,20 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45C1795-70FB-4398-B90E-C9AA5E3C0394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="390" windowWidth="28800" windowHeight="15345"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Periodo Actual</t>
   </si>
@@ -25,9 +47,6 @@
     <t>¿Durante el año correspondiente al corte de la información que está presentando, se dedicó habitualmente a la comercialización de metales preciosos y piedras preciosas?</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>¿Durante el año correspondiente al corte de la información que está presentando, recibió uno o varios aportes de Activos Virtuales iguales o superiores (individualmente o en conjunto) a 100 SMLMV?</t>
   </si>
   <si>
@@ -35,9 +54,6 @@
   </si>
   <si>
     <t>¿Durante el año correspondiente al corte de la información que está presentando, realizó uno o más negocios o transacciones internacionales (individualmente o en conjunto) por un monto igual o superior a 100 SMLMV?</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
   <si>
     <t>¿Durante el año correspondiente al corte de la información que está presentando, firmó uno o más contratos con Entidades Estatales en una cuantía igual o superior  (individual o en conjunto) a 500 SMLMV?</t>
@@ -52,28 +68,28 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Microsoft Sans Serif"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11.00"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
     <font>
-      <color indexed="8"/>
+      <name val="Microsoft Sans Serif"/>
+      <sz val="9.00"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -83,21 +99,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="darkDown">
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9999FF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,32 +136,50 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -151,7 +195,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -161,39 +205,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -226,26 +270,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -278,23 +305,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -304,25 +314,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110%"/>
-                <a:satMod val="105%"/>
-                <a:tint val="67%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="103%"/>
-                <a:tint val="73%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="109%"/>
-                <a:tint val="81%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -330,25 +340,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103%"/>
-                <a:lumMod val="102%"/>
-                <a:tint val="94%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110%"/>
-                <a:lumMod val="100%"/>
-                <a:shade val="100%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99%"/>
-                <a:satMod val="120%"/>
-                <a:shade val="78%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -356,26 +366,26 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -389,7 +399,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63%"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -401,32 +411,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95%"/>
-            <a:satMod val="170%"/>
+            <a:satMod val="170000"/>
+            <a:tint val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:tint val="93%"/>
-                <a:satMod val="150%"/>
-                <a:shade val="98%"/>
-                <a:lumMod val="102%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:tint val="98%"/>
-                <a:satMod val="130%"/>
-                <a:shade val="90%"/>
-                <a:lumMod val="103%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:shade val="63%"/>
-                <a:satMod val="120%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="120000"/>
+                <a:shade val="63000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -435,114 +445,95 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.00" customHeight="1" defaultColWidth="9.20"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="2.70" customWidth="1" hidden="0"/>
+    <col min="2" max="2" width="50.04" customWidth="1" hidden="0"/>
+    <col min="3" max="3" width="14.96" customWidth="1" hidden="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.00" customHeight="true">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.00" customHeight="true">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" ht="38.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" ht="38.25" customHeight="true">
       <c r="A3" s="2"/>
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="51.00" customHeight="true">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="63.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="63.75" customHeight="true">
       <c r="A5" s="2"/>
       <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="51" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="51.00" customHeight="true">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="51.00" customHeight="true">
       <c r="A7" s="2"/>
       <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" ht="63.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="63.75" customHeight="true">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" ht="51" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" ht="51.00" customHeight="true">
       <c r="A9" s="2"/>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="5"/>
     </row>
@@ -550,6 +541,9 @@
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <headerFooter alignWithMargins="1"/>
 </worksheet>
 </file>